--- a/Sergio i Dome/PB_SergioCastañeirasMorales_DomènecHuertaestradé_T18.xlsx
+++ b/Sergio i Dome/PB_SergioCastañeirasMorales_DomènecHuertaestradé_T18.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sergio/Desktop/University/5nto/LACE/LACE/Sergio i Dome/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D2F0AF4-EAB5-144E-AF6C-750CCE1970FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84CDCC98-C765-B148-971B-8A6C743415E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="860" windowWidth="34200" windowHeight="21380" xr2:uid="{C1122783-245A-4FED-BDEB-F09B1698DCDF}"/>
+    <workbookView xWindow="0" yWindow="840" windowWidth="34200" windowHeight="21400" xr2:uid="{C1122783-245A-4FED-BDEB-F09B1698DCDF}"/>
   </bookViews>
   <sheets>
     <sheet name="Pràctica A" sheetId="1" r:id="rId1"/>
@@ -351,11 +351,11 @@
     <t>u_ n</t>
   </si>
   <si>
-    <t>( ± )</t>
+    <t xml:space="preserve">S_0 </t>
   </si>
   <si>
     <r>
-      <t>( ± ) ppm</t>
+      <t>(0.18 ± 0.01) ppm</t>
     </r>
     <r>
       <rPr>
@@ -369,10 +369,10 @@
     </r>
   </si>
   <si>
-    <t>S_0 amb LiCl</t>
-  </si>
-  <si>
-    <t>S_0 sense LiCl</t>
+    <t>( 0.20 ± 0.02)</t>
+  </si>
+  <si>
+    <t>(5 ± 1) ppm</t>
   </si>
 </sst>
 </file>
@@ -647,9 +647,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -666,12 +663,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -758,6 +749,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -890,6 +890,89 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="3.0434449618342383E-2"/>
+                  <c:y val="0.20390428561607468"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:pPr>
+                      <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                        <a:solidFill>
+                          <a:schemeClr val="tx1">
+                            <a:lumMod val="65000"/>
+                            <a:lumOff val="35000"/>
+                          </a:schemeClr>
+                        </a:solidFill>
+                        <a:latin typeface="+mn-lt"/>
+                        <a:ea typeface="+mn-ea"/>
+                        <a:cs typeface="+mn-cs"/>
+                      </a:defRPr>
+                    </a:pPr>
+                    <a:r>
+                      <a:rPr lang="en-US" baseline="0"/>
+                      <a:t>Senyal AES = 0.1823*[K+] + 0.2047</a:t>
+                    </a:r>
+                    <a:br>
+                      <a:rPr lang="en-US" baseline="0"/>
+                    </a:br>
+                    <a:r>
+                      <a:rPr lang="en-US" baseline="0"/>
+                      <a:t>R² = 0.9944</a:t>
+                    </a:r>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-ES"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
           <c:xVal>
             <c:numRef>
               <c:f>'Pràctica A'!$D$38:$D$42</c:f>
@@ -897,19 +980,19 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>0.50823204935622313</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>1.5246961480686694</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>2.0329281974248925</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>3.0493922961373388</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>4.065856394849785</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -920,6 +1003,21 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.2752</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.50580000000000003</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.5907</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.74939999999999996</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.94059999999999999</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
@@ -1850,7 +1948,7 @@
           </a:r>
           <a:r>
             <a:rPr lang="en-GB" sz="1100" baseline="0"/>
-            <a:t> en la primera planta de la torre C7 parell de la facultat de ciències de la Universitat Autònoma de Barcelona el dia 13 maig de 2026 a les 15:40 h</a:t>
+            <a:t> en la primera planta de la torre C7 parell de la facultat de ciències de la Universitat Autònoma de Barcelona el dia 13 maig de 2026 a les 14:40 h</a:t>
           </a:r>
           <a:endParaRPr lang="en-GB" sz="1100"/>
         </a:p>
@@ -1861,127 +1959,416 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>67733</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>25400</xdr:rowOff>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>426053</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>1016000</xdr:colOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>612624</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>204108</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="TextBox 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1A1ABE25-7BDD-DBD7-0852-DE8ED7FFE7B5}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="67733" y="2497667"/>
-          <a:ext cx="6155267" cy="1752600"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-        <a:ln w="9525" cmpd="sng">
-          <a:solidFill>
-            <a:schemeClr val="lt1">
-              <a:shade val="50000"/>
-            </a:schemeClr>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-GB" b="0"/>
-            <a:t>Per a la detecció de la concentració de</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" b="0" baseline="0"/>
-            <a:t> l'ió postassi</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" b="0"/>
-            <a:t> en una mostra d’aigua</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" b="0" baseline="0"/>
-            <a:t> potable</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" b="0"/>
-            <a:t>, fem servir el model 55 AA de la marca Agilent, que permet quantificar la mostra mitjançant espectroscòpia d’emissió atòmica atòmica.</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:br>
-            <a:rPr lang="en-GB" b="0"/>
-          </a:br>
-          <a:r>
-            <a:rPr lang="en-GB" b="0"/>
-            <a:t>Donat</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" b="0" baseline="0"/>
-            <a:t> que fem servir l'aparell en mode d'emissió no es fa ús de cap làmpada, si més no és clau ajustar el detector en el rang del potassi amb el patró més concentrat.</a:t>
-          </a:r>
-          <a:br>
-            <a:rPr lang="en-GB" b="0"/>
-          </a:br>
-          <a:endParaRPr lang="en-GB" b="0"/>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-GB" b="0"/>
-            <a:t>Després de realitzar un calibratge amb solucions patró de concentració coneguda de potassi, i mitjançant la llei de Lambert-Beer, podem quantificar la concentració de coure a partir d’una recta de regressió.</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:br>
-            <a:rPr lang="en-GB" b="0"/>
-          </a:br>
-          <a:endParaRPr lang="en-GB" b="0"/>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-GB" b="0"/>
-            <a:t>Nota: És essencial mantenir l’equip net i lliure de residus, ja que, en tractar-se d’una tècnica de quantificació atòmica, la presència d’interferències pot provocar desviacions significatives en els resultats.</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="3" name="TextBox 2">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1A1ABE25-7BDD-DBD7-0852-DE8ED7FFE7B5}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="0" y="4878613"/>
+              <a:ext cx="8610600" cy="3383947"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:ln w="9525" cmpd="sng">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:shade val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="ctr"/>
+              <a:r>
+                <a:rPr lang="en-GB" b="0"/>
+                <a:t>Per a la detecció de la concentració de l’ió potassi en una mostra d’aigua potable, fem servir el model 55 AA de la marca Agilent, que permet quantificar mitjançant espectroscòpia d’emissió atòmica.</a:t>
+              </a:r>
+            </a:p>
+            <a:p>
+              <a:pPr algn="ctr"/>
+              <a:endParaRPr lang="en-GB" b="0"/>
+            </a:p>
+            <a:p>
+              <a:pPr algn="ctr"/>
+              <a:r>
+                <a:rPr lang="en-GB" b="0"/>
+                <a:t>Com que utilitzem l’aparell en mode d’emissió, no es fa ús de cap làmpada. Tanmateix, és fonamental ajustar el detector dins el rang del potassi, utilitzant el patró de concentració més elevada per garantir una detecció precisa.</a:t>
+              </a:r>
+            </a:p>
+            <a:p>
+              <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="ctr" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+                <a:lnSpc>
+                  <a:spcPct val="100000"/>
+                </a:lnSpc>
+                <a:spcBef>
+                  <a:spcPts val="0"/>
+                </a:spcBef>
+                <a:spcAft>
+                  <a:spcPts val="0"/>
+                </a:spcAft>
+                <a:buClrTx/>
+                <a:buSzTx/>
+                <a:buFontTx/>
+                <a:buNone/>
+                <a:tabLst/>
+                <a:defRPr/>
+              </a:pPr>
+              <a:br>
+                <a:rPr lang="en-GB" b="0"/>
+              </a:br>
+              <a:r>
+                <a:rPr lang="en-GB" b="0"/>
+                <a:t>Nota: És essencial mantenir l’equip net i lliure de residus, ja que es tracta d’una tècnica de quantificació atòmica molt sensible. La presència d’interferències pot provocar desviacions significatives en els resultats obtinguts. </a:t>
+              </a:r>
+              <a:br>
+                <a:rPr lang="en-GB" b="0"/>
+              </a:br>
+              <a:endParaRPr lang="en-GB" b="0"/>
+            </a:p>
+            <a:p>
+              <a:pPr algn="ctr"/>
+              <a:r>
+                <a:rPr lang="en-GB" b="0"/>
+                <a:t>Després de realitzar el calibratge amb solucions patró de concentració coneguda de potassi, i aplicant la llei de Lambert-Beer, es pot quantificar la concentració d’aquest element mitjançant la construcció d’una recta de regressió.</a:t>
+              </a:r>
+              <a:br>
+                <a:rPr lang="en-GB" b="0"/>
+              </a:br>
+              <a:endParaRPr lang="en-GB" b="0"/>
+            </a:p>
+            <a:p>
+              <a:pPr algn="ctr"/>
+              <a:r>
+                <a:rPr lang="en-GB" b="0"/>
+                <a:t>S’utilitza un tampó de clorur de liti en totes les substàncies analitzades amb l’objectiu d’afavorir la presència de potassi elemental en la flama i, per tant, augmentar la sensibilitat del mètode. Això és degut al fet que, en ionitzar-se, el liti allibera electrons, afavorint la reacció,</a:t>
+              </a:r>
+            </a:p>
+            <a:p>
+              <a:pPr algn="ctr"/>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:r>
+                      <a:rPr lang="es-ES" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>𝐾</m:t>
+                    </m:r>
+                    <m:r>
+                      <a:rPr lang="es-ES" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                        <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>⟷</m:t>
+                    </m:r>
+                    <m:sSup>
+                      <m:sSupPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="es-ES" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSupPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="es-ES" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝐾</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sup>
+                        <m:r>
+                          <a:rPr lang="es-ES" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>+</m:t>
+                        </m:r>
+                      </m:sup>
+                    </m:sSup>
+                    <m:r>
+                      <a:rPr lang="es-ES" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                        <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>+</m:t>
+                    </m:r>
+                    <m:sSup>
+                      <m:sSupPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="es-ES" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSupPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="es-ES" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑒</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sup>
+                        <m:r>
+                          <a:rPr lang="es-ES" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>−</m:t>
+                        </m:r>
+                      </m:sup>
+                    </m:sSup>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="es-ES" b="0">
+                <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+              </a:endParaRPr>
+            </a:p>
+            <a:p>
+              <a:pPr algn="ctr"/>
+              <a:r>
+                <a:rPr lang="en-GB" b="0"/>
+                <a:t>cap a la generació de potassi</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-GB" b="0" baseline="0"/>
+                <a:t> elemental.</a:t>
+              </a:r>
+              <a:endParaRPr lang="en-GB" b="0"/>
+            </a:p>
+            <a:p>
+              <a:pPr algn="ctr"/>
+              <a:endParaRPr lang="en-GB" b="0"/>
+            </a:p>
+            <a:p>
+              <a:pPr algn="ctr"/>
+              <a:r>
+                <a:rPr lang="en-GB" b="0"/>
+                <a:t>Nota: El color de la flama canvia a un vermell intens en presència de liti, cosa que reflecteix qualitativament la presència d’aquest element en la mostra o solució patró. </a:t>
+              </a:r>
+              <a:br>
+                <a:rPr lang="en-GB" b="0"/>
+              </a:br>
+              <a:endParaRPr lang="en-GB" b="0"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="3" name="TextBox 2">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1A1ABE25-7BDD-DBD7-0852-DE8ED7FFE7B5}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="0" y="4878613"/>
+              <a:ext cx="8610600" cy="3383947"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:ln w="9525" cmpd="sng">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:shade val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="ctr"/>
+              <a:r>
+                <a:rPr lang="en-GB" b="0"/>
+                <a:t>Per a la detecció de la concentració de l’ió potassi en una mostra d’aigua potable, fem servir el model 55 AA de la marca Agilent, que permet quantificar mitjançant espectroscòpia d’emissió atòmica.</a:t>
+              </a:r>
+            </a:p>
+            <a:p>
+              <a:pPr algn="ctr"/>
+              <a:endParaRPr lang="en-GB" b="0"/>
+            </a:p>
+            <a:p>
+              <a:pPr algn="ctr"/>
+              <a:r>
+                <a:rPr lang="en-GB" b="0"/>
+                <a:t>Com que utilitzem l’aparell en mode d’emissió, no es fa ús de cap làmpada. Tanmateix, és fonamental ajustar el detector dins el rang del potassi, utilitzant el patró de concentració més elevada per garantir una detecció precisa.</a:t>
+              </a:r>
+            </a:p>
+            <a:p>
+              <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="ctr" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+                <a:lnSpc>
+                  <a:spcPct val="100000"/>
+                </a:lnSpc>
+                <a:spcBef>
+                  <a:spcPts val="0"/>
+                </a:spcBef>
+                <a:spcAft>
+                  <a:spcPts val="0"/>
+                </a:spcAft>
+                <a:buClrTx/>
+                <a:buSzTx/>
+                <a:buFontTx/>
+                <a:buNone/>
+                <a:tabLst/>
+                <a:defRPr/>
+              </a:pPr>
+              <a:br>
+                <a:rPr lang="en-GB" b="0"/>
+              </a:br>
+              <a:r>
+                <a:rPr lang="en-GB" b="0"/>
+                <a:t>Nota: És essencial mantenir l’equip net i lliure de residus, ja que es tracta d’una tècnica de quantificació atòmica molt sensible. La presència d’interferències pot provocar desviacions significatives en els resultats obtinguts. </a:t>
+              </a:r>
+              <a:br>
+                <a:rPr lang="en-GB" b="0"/>
+              </a:br>
+              <a:endParaRPr lang="en-GB" b="0"/>
+            </a:p>
+            <a:p>
+              <a:pPr algn="ctr"/>
+              <a:r>
+                <a:rPr lang="en-GB" b="0"/>
+                <a:t>Després de realitzar el calibratge amb solucions patró de concentració coneguda de potassi, i aplicant la llei de Lambert-Beer, es pot quantificar la concentració d’aquest element mitjançant la construcció d’una recta de regressió.</a:t>
+              </a:r>
+              <a:br>
+                <a:rPr lang="en-GB" b="0"/>
+              </a:br>
+              <a:endParaRPr lang="en-GB" b="0"/>
+            </a:p>
+            <a:p>
+              <a:pPr algn="ctr"/>
+              <a:r>
+                <a:rPr lang="en-GB" b="0"/>
+                <a:t>S’utilitza un tampó de clorur de liti en totes les substàncies analitzades amb l’objectiu d’afavorir la presència de potassi elemental en la flama i, per tant, augmentar la sensibilitat del mètode. Això és degut al fet que, en ionitzar-se, el liti allibera electrons, afavorint la reacció,</a:t>
+              </a:r>
+            </a:p>
+            <a:p>
+              <a:pPr algn="ctr"/>
+              <a:r>
+                <a:rPr lang="es-ES" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝐾</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="es-ES" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>⟷𝐾^++𝑒^−</a:t>
+              </a:r>
+              <a:endParaRPr lang="es-ES" b="0">
+                <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+              </a:endParaRPr>
+            </a:p>
+            <a:p>
+              <a:pPr algn="ctr"/>
+              <a:r>
+                <a:rPr lang="en-GB" b="0"/>
+                <a:t>cap a la generació de potassi</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-GB" b="0" baseline="0"/>
+                <a:t> elemental.</a:t>
+              </a:r>
+              <a:endParaRPr lang="en-GB" b="0"/>
+            </a:p>
+            <a:p>
+              <a:pPr algn="ctr"/>
+              <a:endParaRPr lang="en-GB" b="0"/>
+            </a:p>
+            <a:p>
+              <a:pPr algn="ctr"/>
+              <a:r>
+                <a:rPr lang="en-GB" b="0"/>
+                <a:t>Nota: El color de la flama canvia a un vermell intens en presència de liti, cosa que reflecteix qualitativament la presència d’aquest element en la mostra o solució patró. </a:t>
+              </a:r>
+              <a:br>
+                <a:rPr lang="en-GB" b="0"/>
+              </a:br>
+              <a:endParaRPr lang="en-GB" b="0"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
@@ -2027,13 +2414,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>8467</xdr:colOff>
       <xdr:row>59</xdr:row>
-      <xdr:rowOff>16933</xdr:rowOff>
+      <xdr:rowOff>16932</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>855134</xdr:colOff>
-      <xdr:row>61</xdr:row>
-      <xdr:rowOff>279400</xdr:rowOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>7559</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2048,8 +2435,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1981200" y="18415000"/>
-          <a:ext cx="5139267" cy="855133"/>
+          <a:off x="1973943" y="20752706"/>
+          <a:ext cx="5125358" cy="1162353"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2086,8 +2473,13 @@
           <a:pPr algn="ctr"/>
           <a:r>
             <a:rPr lang="en-GB" sz="1100"/>
-            <a:t>Comento comentant</a:t>
-          </a:r>
+            <a:t>Hem</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100" baseline="0"/>
+            <a:t> fet una prova de la senyal emessa per la mostra i patrons en absència de liti. El resultat ha estat una senyal molt baixa, doncs el potassi en trobar-se majoritariament en estat ionitzat no emet en el rang observat. Ara bé, en afegir el liti la senyal ha augmentat de forma considerable donant lloc a la recta observada.</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-GB" sz="1100"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -2573,6 +2965,134 @@
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
             <a:t>Tot i que aquesta normativa fou revocada al 22 de febrer de 2003.</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>45357</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>60475</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>861785</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>287261</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="TextBox 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C70BE5E1-6194-A070-E62E-3CBA31B057B7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="45357" y="24031725"/>
+          <a:ext cx="7060595" cy="2789465"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" b="0"/>
+            <a:t>Per una banda, hem pogut constatar que el contingut de l’ió potassi a l’aigua compleix amb les normatives establertes anteriorment. Per una altra, s’ha evidenciat el paper clau del tampó de clorur de liti (LiCl) durant la pràctica, i com contribueix a augmentar la sensibilitat de l’aparell.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr lang="en-GB" b="0"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" b="0"/>
+            <a:t>A més, hem observat que, a diferència de la tècnica d’absorció atòmica, en aquest cas no és necessari fer servir una làmpada específica que emeti en la longitud d’ona desitjada. Això és possible perquè l’excitació dels àtoms de potassi es produeix de manera eficient a la temperatura de la flama (aproximadament 1200 °C).</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-GB" b="0"/>
+          </a:br>
+          <a:endParaRPr lang="en-GB" b="0"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" b="0"/>
+            <a:t>Cal remarcar que aquest fet no és extrapolable a tots els elements: en el cas del coure</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" b="0" baseline="0"/>
+            <a:t> (</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" b="0"/>
+            <a:t>com es el</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" b="0" baseline="0"/>
+            <a:t> cas </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" b="0"/>
+            <a:t> d'una pràctica anterior), aquesta temperatura no és suficient per excitar els seus àtoms, i per tant no es genera senyal mitjançant el mètode d’emissió atòmica,</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" b="0" baseline="0"/>
+            <a:t> fent necessari el mètode d'absorció atòmica i una làmpada que emeti en el rang desitjat de longitud d'ona</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" b="0"/>
+            <a:t>.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr lang="en-GB" b="0"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" b="0"/>
+            <a:t>Així doncs, aquesta pràctica ens ha permès comprendre millor la utilitat i el funcionament de l’espectroscòpia d’emissió atòmica, alhora que hem consolidat coneixements adquirits en sessions anteriors basades en l’absorció atòmica.</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -2879,7 +3399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{953B08C8-5267-41A1-8A30-44F36ECBD8D8}">
-  <dimension ref="A1:M71"/>
+  <dimension ref="A1:N71"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="23.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="25.83203125" style="2" customWidth="1"/>
@@ -2898,7 +3418,7 @@
       <c r="E1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="F1" s="23">
+      <c r="F1" s="20">
         <v>45790</v>
       </c>
     </row>
@@ -2906,7 +3426,7 @@
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E2" s="4" t="s">
@@ -2957,7 +3477,9 @@
       <c r="A20" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B20" s="7"/>
+      <c r="B20" s="7">
+        <v>0.48459999999999998</v>
+      </c>
       <c r="C20" s="1" t="s">
         <v>27</v>
       </c>
@@ -2966,15 +3488,17 @@
       <c r="A21" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B21" s="24"/>
+      <c r="B21" s="21">
+        <v>250</v>
+      </c>
     </row>
     <row r="22" spans="1:3" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B22" s="25" t="e">
+      <c r="B22" s="22">
         <f>B20*(39.098/74.56)*10^3/(B21*10^(-3))</f>
-        <v>#DIV/0!</v>
+        <v>1016.4640987124462</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>5</v>
@@ -2989,13 +3513,17 @@
       <c r="A27" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="26"/>
+      <c r="B27" s="23">
+        <v>0.27729999999999999</v>
+      </c>
     </row>
     <row r="28" spans="1:3" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B28" s="24"/>
+      <c r="B28" s="21">
+        <v>250</v>
+      </c>
       <c r="C28" s="1" t="s">
         <v>40</v>
       </c>
@@ -3004,9 +3532,9 @@
       <c r="A29" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B29" s="24" t="e">
+      <c r="B29" s="21">
         <f>B27*(6.939/42.39)*10^3/(B28*10^(-3))</f>
-        <v>#DIV/0!</v>
+        <v>181.56968152866241</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>5</v>
@@ -3021,9 +3549,9 @@
       <c r="A32" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B32" s="27" t="e">
-        <f>B29/2</f>
-        <v>#DIV/0!</v>
+      <c r="B32" s="24">
+        <f>B29*B33/25</f>
+        <v>72.627872611464966</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>5</v>
@@ -3033,9 +3561,8 @@
       <c r="A33" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B33" s="28">
-        <f>25/2</f>
-        <v>12.5</v>
+      <c r="B33" s="25">
+        <v>10</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>40</v>
@@ -3062,126 +3589,174 @@
       <c r="E37" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="J37" s="37" t="s">
+      <c r="J37" s="34" t="s">
         <v>51</v>
       </c>
-      <c r="K37" s="37"/>
-      <c r="L37" s="37"/>
-      <c r="M37" s="37"/>
+      <c r="K37" s="34"/>
+      <c r="L37" s="34"/>
+      <c r="M37" s="34"/>
     </row>
     <row r="38" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="29" t="e">
+      <c r="A38" s="26">
+        <f>$B$22/10/10/4</f>
+        <v>2.5411602467811156</v>
+      </c>
+      <c r="B38" s="21">
+        <v>5</v>
+      </c>
+      <c r="C38" s="21">
+        <v>25</v>
+      </c>
+      <c r="D38" s="21">
+        <f>A38*B38/C38</f>
+        <v>0.50823204935622313</v>
+      </c>
+      <c r="E38" s="7">
+        <v>0.2752</v>
+      </c>
+      <c r="J38" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="K38" s="28" cm="1">
+        <f t="array" ref="K38:L42">LINEST(E38:E42,D38:D42,1,1)</f>
+        <v>0.1822810977933394</v>
+      </c>
+      <c r="L38" s="28">
+        <v>0.20471917808219159</v>
+      </c>
+      <c r="M38" s="29" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="26">
         <f>$B$22/10/10</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="B38" s="24"/>
-      <c r="C38" s="24"/>
-      <c r="D38" s="24" t="e">
-        <f>A38*B38/C38</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E38" s="7"/>
-      <c r="J38" s="30" t="s">
-        <v>52</v>
-      </c>
-      <c r="K38" s="31" t="e" cm="1">
-        <f t="array" ref="K38">LINEST(E38:E42,D38:D42,1,1)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L38" s="31"/>
-      <c r="M38" s="32" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="29" t="e">
+        <v>10.164640987124463</v>
+      </c>
+      <c r="B39" s="21">
+        <v>3.75</v>
+      </c>
+      <c r="C39" s="21">
+        <v>25</v>
+      </c>
+      <c r="D39" s="21">
+        <f>A39*B39/C39</f>
+        <v>1.5246961480686694</v>
+      </c>
+      <c r="E39" s="7">
+        <v>0.50580000000000003</v>
+      </c>
+      <c r="J39" s="27" t="s">
+        <v>53</v>
+      </c>
+      <c r="K39" s="28">
+        <v>7.9141845247648474E-3</v>
+      </c>
+      <c r="L39" s="28">
+        <v>2.019149569509289E-2</v>
+      </c>
+      <c r="M39" s="29" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="26">
         <f>$B$22/10/10</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="B39" s="24"/>
-      <c r="C39" s="24"/>
-      <c r="D39" s="24" t="e">
-        <f>A39*B39/C39</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E39" s="7"/>
-      <c r="J39" s="30" t="s">
-        <v>53</v>
-      </c>
-      <c r="K39" s="31"/>
-      <c r="L39" s="31"/>
-      <c r="M39" s="32" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="29" t="e">
+        <v>10.164640987124463</v>
+      </c>
+      <c r="B40" s="21">
+        <v>5</v>
+      </c>
+      <c r="C40" s="21">
+        <v>25</v>
+      </c>
+      <c r="D40" s="21">
+        <f>A40*B40/C40</f>
+        <v>2.0329281974248925</v>
+      </c>
+      <c r="E40" s="7">
+        <v>0.5907</v>
+      </c>
+      <c r="J40" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="K40" s="30">
+        <v>0.99437657107024036</v>
+      </c>
+      <c r="L40" s="28">
+        <v>2.1735000076156037E-2</v>
+      </c>
+      <c r="M40" s="29" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="26">
         <f>$B$22/10/10</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="B40" s="24"/>
-      <c r="C40" s="24"/>
-      <c r="D40" s="24" t="e">
-        <f>A40*B40/C40</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E40" s="7"/>
-      <c r="J40" s="30" t="s">
-        <v>44</v>
-      </c>
-      <c r="K40" s="33"/>
-      <c r="L40" s="31"/>
-      <c r="M40" s="32" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="29" t="e">
+        <v>10.164640987124463</v>
+      </c>
+      <c r="B41" s="21">
+        <v>7.5</v>
+      </c>
+      <c r="C41" s="21">
+        <v>25</v>
+      </c>
+      <c r="D41" s="21">
+        <f>A41*B41/C41</f>
+        <v>3.0493922961373388</v>
+      </c>
+      <c r="E41" s="7">
+        <v>0.74939999999999996</v>
+      </c>
+      <c r="J41" s="27" t="s">
+        <v>46</v>
+      </c>
+      <c r="K41" s="29">
+        <v>530.48233568379078</v>
+      </c>
+      <c r="L41" s="29">
+        <v>3</v>
+      </c>
+      <c r="M41" s="29" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="26">
         <f>$B$22/10/10</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="B41" s="24"/>
-      <c r="C41" s="24"/>
-      <c r="D41" s="24" t="e">
-        <f>A41*B41/C41</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E41" s="7"/>
-      <c r="J41" s="30" t="s">
-        <v>46</v>
-      </c>
-      <c r="K41" s="32"/>
-      <c r="L41" s="32"/>
-      <c r="M41" s="32" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="29" t="e">
-        <f>$B$22/10/10</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="B42" s="24"/>
-      <c r="C42" s="24"/>
-      <c r="D42" s="24" t="e">
+        <v>10.164640987124463</v>
+      </c>
+      <c r="B42" s="21">
+        <v>10</v>
+      </c>
+      <c r="C42" s="21">
+        <v>25</v>
+      </c>
+      <c r="D42" s="21">
         <f>A42*B42/C42</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E42" s="7"/>
-      <c r="J42" s="30" t="s">
+        <v>4.065856394849785</v>
+      </c>
+      <c r="E42" s="7">
+        <v>0.94059999999999999</v>
+      </c>
+      <c r="J42" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="K42" s="32"/>
-      <c r="L42" s="32"/>
-      <c r="M42" s="32" t="s">
+      <c r="K42" s="29">
+        <v>0.25060528131506848</v>
+      </c>
+      <c r="L42" s="29">
+        <v>1.4172306849315089E-3</v>
+      </c>
+      <c r="M42" s="29" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="43" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B43" s="21"/>
-      <c r="C43" s="21"/>
-      <c r="D43" s="21"/>
-      <c r="E43" s="21"/>
+      <c r="B43" s="18"/>
+      <c r="C43" s="18"/>
+      <c r="D43" s="18"/>
+      <c r="E43" s="18"/>
     </row>
     <row r="46" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="9" t="s">
@@ -3190,149 +3765,148 @@
       <c r="B46" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C46" s="38" t="s">
+      <c r="C46" s="35" t="s">
         <v>56</v>
       </c>
-      <c r="D46" s="39"/>
+      <c r="D46" s="36"/>
       <c r="E46" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F46" s="29">
+      <c r="F46" s="26">
         <f>L40</f>
-        <v>0</v>
+        <v>2.1735000076156037E-2</v>
       </c>
       <c r="K46" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="L46" s="34" t="e">
+      <c r="L46" s="31">
         <f>AVERAGE(E38:E42)</f>
-        <v>#DIV/0!</v>
+        <v>0.61234</v>
       </c>
     </row>
     <row r="47" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="11"/>
+      <c r="A47" s="10"/>
       <c r="B47" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C47" s="38" t="s">
-        <v>55</v>
-      </c>
-      <c r="D47" s="39"/>
+      <c r="C47" s="35" t="s">
+        <v>57</v>
+      </c>
+      <c r="D47" s="36"/>
       <c r="E47" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F47" s="25">
+      <c r="F47" s="22">
         <f>COUNT(D38:D42)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K47" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="L47" s="35" t="e">
+      <c r="L47" s="32">
         <f>VARPA(D38:D42)*F47</f>
-        <v>#DIV/0!</v>
+        <v>7.5423546269905382</v>
       </c>
     </row>
     <row r="48" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="12"/>
-      <c r="F48" s="13"/>
+      <c r="A48" s="11"/>
+      <c r="F48" s="12"/>
       <c r="K48" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="L48" s="28" t="e">
+        <v>55</v>
+      </c>
+      <c r="L48" s="25">
         <f>L40/K38*SQRT(1+1/F47+(C65-L46)^2/(K38^2*L47))</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="49" spans="1:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="12"/>
-      <c r="F49" s="13"/>
+        <v>0.13063014490214125</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="11"/>
+      <c r="F49" s="12"/>
       <c r="K49" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="L49" s="28" t="e">
-        <f>L40/K38*SQRT(1+1/F47+(C68-L46)^2/(K38^2*L47))</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="50" spans="1:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="12"/>
-      <c r="F50" s="13"/>
-      <c r="K50" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="L50" s="34" t="e">
+      <c r="L49" s="31">
         <f>_xlfn.T.INV.2T(0.05,L41)</f>
-        <v>#NUM!</v>
-      </c>
-    </row>
-    <row r="51" spans="1:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="12"/>
-      <c r="F51" s="13"/>
-    </row>
-    <row r="52" spans="1:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="12"/>
-      <c r="F52" s="13"/>
-    </row>
-    <row r="53" spans="1:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="12"/>
-      <c r="F53" s="13"/>
-    </row>
-    <row r="54" spans="1:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="12"/>
-      <c r="F54" s="13"/>
-    </row>
-    <row r="55" spans="1:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="12"/>
-      <c r="F55" s="13"/>
-    </row>
-    <row r="56" spans="1:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="12"/>
-      <c r="F56" s="13"/>
-    </row>
-    <row r="57" spans="1:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="12"/>
-      <c r="F57" s="13"/>
-    </row>
-    <row r="58" spans="1:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="12"/>
-      <c r="F58" s="13"/>
-    </row>
-    <row r="59" spans="1:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="11"/>
-      <c r="B59" s="14"/>
-      <c r="C59" s="14"/>
-      <c r="D59" s="14"/>
-      <c r="E59" s="14"/>
-      <c r="F59" s="15"/>
-    </row>
-    <row r="60" spans="1:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="40" t="s">
+        <v>3.1824463052837091</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="11"/>
+      <c r="F50" s="12"/>
+    </row>
+    <row r="51" spans="1:14" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="11"/>
+      <c r="F51" s="12"/>
+    </row>
+    <row r="52" spans="1:14" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="11"/>
+      <c r="F52" s="12"/>
+    </row>
+    <row r="53" spans="1:14" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="11"/>
+      <c r="F53" s="12"/>
+    </row>
+    <row r="54" spans="1:14" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="11"/>
+      <c r="F54" s="12"/>
+    </row>
+    <row r="55" spans="1:14" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="11"/>
+      <c r="F55" s="12"/>
+      <c r="M55" s="46"/>
+      <c r="N55" s="46"/>
+    </row>
+    <row r="56" spans="1:14" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="11"/>
+      <c r="F56" s="12"/>
+      <c r="M56" s="46"/>
+      <c r="N56" s="47"/>
+    </row>
+    <row r="57" spans="1:14" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="11"/>
+      <c r="F57" s="12"/>
+      <c r="M57" s="46"/>
+      <c r="N57" s="46"/>
+    </row>
+    <row r="58" spans="1:14" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="11"/>
+      <c r="F58" s="12"/>
+    </row>
+    <row r="59" spans="1:14" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="10"/>
+      <c r="B59" s="13"/>
+      <c r="C59" s="13"/>
+      <c r="D59" s="13"/>
+      <c r="E59" s="13"/>
+      <c r="F59" s="14"/>
+    </row>
+    <row r="60" spans="1:14" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="B60" s="43"/>
-      <c r="C60" s="40"/>
-      <c r="D60" s="40"/>
-      <c r="E60" s="40"/>
-      <c r="F60" s="44"/>
-    </row>
-    <row r="61" spans="1:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="41"/>
-      <c r="B61" s="45"/>
-      <c r="C61" s="41"/>
-      <c r="D61" s="41"/>
-      <c r="E61" s="41"/>
-      <c r="F61" s="46"/>
-    </row>
-    <row r="62" spans="1:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="42"/>
-      <c r="B62" s="47"/>
-      <c r="C62" s="42"/>
-      <c r="D62" s="42"/>
-      <c r="E62" s="42"/>
-      <c r="F62" s="48"/>
-    </row>
-    <row r="64" spans="1:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B60" s="40"/>
+      <c r="C60" s="37"/>
+      <c r="D60" s="37"/>
+      <c r="E60" s="37"/>
+      <c r="F60" s="41"/>
+    </row>
+    <row r="61" spans="1:14" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="38"/>
+      <c r="B61" s="42"/>
+      <c r="C61" s="38"/>
+      <c r="D61" s="38"/>
+      <c r="E61" s="38"/>
+      <c r="F61" s="43"/>
+    </row>
+    <row r="62" spans="1:14" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="39"/>
+      <c r="B62" s="44"/>
+      <c r="C62" s="39"/>
+      <c r="D62" s="39"/>
+      <c r="E62" s="39"/>
+      <c r="F62" s="45"/>
+    </row>
+    <row r="64" spans="1:14" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B64" s="1" t="s">
         <v>8</v>
       </c>
@@ -3350,54 +3924,68 @@
       <c r="A65" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="B65" s="1"/>
-      <c r="C65" s="1"/>
-      <c r="D65" s="1"/>
-      <c r="E65" s="1"/>
+      <c r="B65" s="1">
+        <f>25/10</f>
+        <v>2.5</v>
+      </c>
+      <c r="C65" s="1">
+        <v>0.60540000000000005</v>
+      </c>
+      <c r="D65" s="32">
+        <f>(C65-L38)/K38*B65</f>
+        <v>5.4953698815781635</v>
+      </c>
+      <c r="E65" s="32">
+        <f>L48*L49*B65</f>
+        <v>1.0393085550062373</v>
+      </c>
     </row>
     <row r="67" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="19" t="s">
+      <c r="A67" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="B67" s="16"/>
-      <c r="C67" s="17"/>
-      <c r="D67" s="18"/>
-      <c r="E67" s="10"/>
+      <c r="B67" s="15"/>
+      <c r="C67" s="35" t="s">
+        <v>58</v>
+      </c>
+      <c r="D67" s="48"/>
+      <c r="E67" s="36"/>
     </row>
     <row r="69" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A69" s="20" t="s">
+      <c r="A69" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="B69" s="21"/>
-      <c r="C69" s="21"/>
-      <c r="D69" s="21"/>
-      <c r="E69" s="21"/>
-      <c r="F69" s="21"/>
-    </row>
-    <row r="70" spans="1:6" ht="130.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="36"/>
-      <c r="B70" s="36"/>
-      <c r="C70" s="36"/>
-      <c r="D70" s="36"/>
-      <c r="E70" s="36"/>
-      <c r="F70" s="36"/>
+      <c r="B69" s="18"/>
+      <c r="C69" s="18"/>
+      <c r="D69" s="18"/>
+      <c r="E69" s="18"/>
+      <c r="F69" s="18"/>
+    </row>
+    <row r="70" spans="1:6" ht="86" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A70" s="33"/>
+      <c r="B70" s="33"/>
+      <c r="C70" s="33"/>
+      <c r="D70" s="33"/>
+      <c r="E70" s="33"/>
+      <c r="F70" s="33"/>
     </row>
     <row r="71" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="21"/>
-      <c r="B71" s="21"/>
-      <c r="C71" s="21"/>
-      <c r="D71" s="21"/>
-      <c r="E71" s="21"/>
-      <c r="F71" s="21"/>
+      <c r="A71" s="18"/>
+      <c r="B71" s="18"/>
+      <c r="C71" s="18"/>
+      <c r="D71" s="18"/>
+      <c r="E71" s="18"/>
+      <c r="F71" s="18"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
     <mergeCell ref="A70:F70"/>
     <mergeCell ref="J37:M37"/>
     <mergeCell ref="C46:D46"/>
     <mergeCell ref="C47:D47"/>
     <mergeCell ref="A60:A62"/>
     <mergeCell ref="B60:F62"/>
+    <mergeCell ref="C67:E67"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Sergio i Dome/PB_SergioCastañeirasMorales_DomènecHuertaestradé_T18.xlsx
+++ b/Sergio i Dome/PB_SergioCastañeirasMorales_DomènecHuertaestradé_T18.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10329"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10309"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sergio/Desktop/University/5nto/LACE/LACE/Sergio i Dome/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/deumenec/Documents/Uni/LACE/Sergio i Dome/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D2F0AF4-EAB5-144E-AF6C-750CCE1970FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2132F7A7-D57F-2341-A802-29460DB42103}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="860" windowWidth="34200" windowHeight="21380" xr2:uid="{C1122783-245A-4FED-BDEB-F09B1698DCDF}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{C1122783-245A-4FED-BDEB-F09B1698DCDF}"/>
   </bookViews>
   <sheets>
     <sheet name="Pràctica A" sheetId="1" r:id="rId1"/>
@@ -780,7 +780,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
